--- a/Интеллектуальный анализ данных/Лабораторные работы/ЛР4/Лабораторная работа 4.xlsx
+++ b/Интеллектуальный анализ данных/Лабораторные работы/ЛР4/Лабораторная работа 4.xlsx
@@ -1,33 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Honor\OneDrive\Рабочий стол\Lessons\6-semestr\Интеллектуальный анализ данных\Лабораторные работы\ЛР4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\6 semestr\6-semestr\Интеллектуальный анализ данных\Лабораторные работы\ЛР4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D530F19D-55EB-4C44-BB8F-6343A7CEBB5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{288A3CC2-43F5-4008-A4AE-25E0CBB0F214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1824" yWindow="2484" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2655" yWindow="2715" windowWidth="25425" windowHeight="11340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -111,6 +102,913 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Численная</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU" baseline="0"/>
+              <a:t> мера качества классификации</a:t>
+            </a:r>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.12045822397200349"/>
+          <c:y val="4.1666666666666664E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$G$2:$G$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>2.5445169921807325</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.81376108437131056</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.42460425400618368</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.26699185372588319</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.18407360667130587</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.13505007193817112</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.10407875710312325</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8.2601397636234572E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.7123723734149196E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2159-483C-B509-8EBA7E30B50F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="703098416"/>
+        <c:axId val="703099496"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="703098416"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="703099496"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="703099496"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="703098416"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>290512</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>157162</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>595312</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>42862</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Диаграмма 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E551CF84-1CB2-A355-C51A-7361B2B8E07D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -377,14 +1275,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -407,7 +1305,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>2</v>
       </c>
@@ -428,8 +1326,12 @@
         <f>(1/A2)*SUM($D$2:D2)</f>
         <v>44876.964999999997</v>
       </c>
+      <c r="G2">
+        <f>E2/F2</f>
+        <v>2.5445169921807325</v>
+      </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>3</v>
       </c>
@@ -450,8 +1352,12 @@
         <f>(1/A3)*SUM($D$2:D3)</f>
         <v>74961.776666666658</v>
       </c>
+      <c r="G3">
+        <f t="shared" ref="G3:G10" si="0">E3/F3</f>
+        <v>0.81376108437131056</v>
+      </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>4</v>
       </c>
@@ -472,8 +1378,12 @@
         <f>(1/A4)*SUM($D$2:D4)</f>
         <v>93443.407500000001</v>
       </c>
+      <c r="G4">
+        <f t="shared" si="0"/>
+        <v>0.42460425400618368</v>
+      </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>5</v>
       </c>
@@ -494,8 +1404,12 @@
         <f>(1/A5)*SUM($D$2:D5)</f>
         <v>106360.52600000001</v>
       </c>
+      <c r="G5">
+        <f t="shared" si="0"/>
+        <v>0.26699185372588319</v>
+      </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>6</v>
       </c>
@@ -516,8 +1430,12 @@
         <f>(1/A6)*SUM($D$2:D6)</f>
         <v>116391.80500000001</v>
       </c>
+      <c r="G6">
+        <f t="shared" si="0"/>
+        <v>0.18407360667130587</v>
+      </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>7</v>
       </c>
@@ -538,8 +1456,12 @@
         <f>(1/A7)*SUM($D$2:D7)</f>
         <v>124406.10428571429</v>
       </c>
+      <c r="G7">
+        <f t="shared" si="0"/>
+        <v>0.13505007193817112</v>
+      </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>8</v>
       </c>
@@ -560,8 +1482,12 @@
         <f>(1/A8)*SUM($D$2:D8)</f>
         <v>130802.84125000001</v>
       </c>
+      <c r="G8">
+        <f t="shared" si="0"/>
+        <v>0.10407875710312325</v>
+      </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>9</v>
       </c>
@@ -582,8 +1508,12 @@
         <f>(1/A9)*SUM($D$2:D9)</f>
         <v>136261.97</v>
       </c>
+      <c r="G9">
+        <f t="shared" si="0"/>
+        <v>8.2601397636234572E-2</v>
+      </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>10</v>
       </c>
@@ -604,8 +1534,13 @@
         <f>(1/A10)*SUM($D$2:D10)</f>
         <v>140969.073</v>
       </c>
+      <c r="G10">
+        <f t="shared" si="0"/>
+        <v>6.7123723734149196E-2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Интеллектуальный анализ данных/Лабораторные работы/ЛР4/Лабораторная работа 4.xlsx
+++ b/Интеллектуальный анализ данных/Лабораторные работы/ЛР4/Лабораторная работа 4.xlsx
@@ -1,24 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\6 semestr\6-semestr\Интеллектуальный анализ данных\Лабораторные работы\ЛР4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Honor\OneDrive\Рабочий стол\Lessons\6-semestr\Интеллектуальный анализ данных\Лабораторные работы\ЛР4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{288A3CC2-43F5-4008-A4AE-25E0CBB0F214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686DEA9E-1B67-40BB-8F83-EE582CFD20E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2655" yWindow="2715" windowWidth="25425" windowHeight="11340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -81,12 +90,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -207,6 +217,42 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Лист1!$A$2:$A$10</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
           <c:val>
             <c:numRef>
               <c:f>Лист1!$G$2:$G$10</c:f>
@@ -269,7 +315,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1275,14 +1321,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -1305,8 +1351,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
         <v>2</v>
       </c>
       <c r="B2" s="1">
@@ -1331,8 +1377,8 @@
         <v>2.5445169921807325</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
         <v>3</v>
       </c>
       <c r="B3" s="1">
@@ -1357,8 +1403,8 @@
         <v>0.81376108437131056</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
         <v>4</v>
       </c>
       <c r="B4" s="1">
@@ -1383,8 +1429,8 @@
         <v>0.42460425400618368</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
         <v>5</v>
       </c>
       <c r="B5" s="1">
@@ -1409,8 +1455,8 @@
         <v>0.26699185372588319</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
         <v>6</v>
       </c>
       <c r="B6" s="1">
@@ -1435,8 +1481,8 @@
         <v>0.18407360667130587</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
         <v>7</v>
       </c>
       <c r="B7" s="1">
@@ -1461,8 +1507,8 @@
         <v>0.13505007193817112</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
         <v>8</v>
       </c>
       <c r="B8" s="1">
@@ -1487,8 +1533,8 @@
         <v>0.10407875710312325</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
         <v>9</v>
       </c>
       <c r="B9" s="1">
@@ -1513,8 +1559,8 @@
         <v>8.2601397636234572E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
         <v>10</v>
       </c>
       <c r="B10" s="1">
@@ -1541,6 +1587,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Интеллектуальный анализ данных/Лабораторные работы/ЛР4/Лабораторная работа 4.xlsx
+++ b/Интеллектуальный анализ данных/Лабораторные работы/ЛР4/Лабораторная работа 4.xlsx
@@ -1,33 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Honor\OneDrive\Рабочий стол\Lessons\6-semestr\Интеллектуальный анализ данных\Лабораторные работы\ЛР4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\6 semestr\Интеллектуальный анализ данных\Лабораторные работы\ЛР4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686DEA9E-1B67-40BB-8F83-EE582CFD20E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E75D0D4-7F20-41C6-BA80-93411B10B97E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1155" yWindow="60" windowWidth="25425" windowHeight="11340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -260,31 +251,31 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>2.5445169921807325</c:v>
+                  <c:v>1.4036345994124966</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.81376108437131056</c:v>
+                  <c:v>0.38984816375434017</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.42460425400618368</c:v>
+                  <c:v>0.1786832402430425</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.26699185372588319</c:v>
+                  <c:v>0.10221336713300791</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.18407360667130587</c:v>
+                  <c:v>6.6856973072943929E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.13505007193817112</c:v>
+                  <c:v>4.7320794738138036E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.10407875710312325</c:v>
+                  <c:v>3.5537153165353184E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8.2601397636234572E-2</c:v>
+                  <c:v>2.7653018504256742E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>6.7123723734149196E-2</c:v>
+                  <c:v>2.2215118344380842E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1321,14 +1312,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -1351,238 +1343,238 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>114190.2</v>
+        <v>10122158693</v>
       </c>
       <c r="C2" s="1">
         <v>2</v>
       </c>
       <c r="D2" s="1">
-        <v>89753.93</v>
+        <v>14422783105</v>
       </c>
       <c r="E2">
         <f>(2/(A2*(A2-1)))*SUM($B$2:B2)</f>
-        <v>114190.2</v>
+        <v>10122158693</v>
       </c>
       <c r="F2">
         <f>(1/A2)*SUM($D$2:D2)</f>
-        <v>44876.964999999997</v>
+        <v>7211391552.5</v>
       </c>
       <c r="G2">
         <f>E2/F2</f>
-        <v>2.5445169921807325</v>
+        <v>1.4036345994124966</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>3</v>
       </c>
       <c r="B3" s="1">
-        <v>68812.73</v>
+        <v>3647403679</v>
       </c>
       <c r="C3" s="1">
         <v>3</v>
       </c>
       <c r="D3" s="1">
-        <v>135131.4</v>
+        <v>20897538118</v>
       </c>
       <c r="E3">
         <f>(2/(A3*(A3-1)))*SUM($B$2:B3)</f>
-        <v>61000.976666666662</v>
+        <v>4589854124</v>
       </c>
       <c r="F3">
         <f>(1/A3)*SUM($D$2:D3)</f>
-        <v>74961.776666666658</v>
+        <v>11773440407.666666</v>
       </c>
       <c r="G3">
         <f t="shared" ref="G3:G10" si="0">E3/F3</f>
-        <v>0.81376108437131056</v>
+        <v>0.38984816375434017</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>4</v>
       </c>
       <c r="B4" s="1">
-        <v>55055.88</v>
+        <v>1794772690</v>
       </c>
       <c r="C4" s="1">
         <v>4</v>
       </c>
       <c r="D4" s="1">
-        <v>148888.29999999999</v>
+        <v>22750169107</v>
       </c>
       <c r="E4">
         <f>(2/(A4*(A4-1)))*SUM($B$2:B4)</f>
-        <v>39676.468333333331</v>
+        <v>2594055843.6666665</v>
       </c>
       <c r="F4">
         <f>(1/A4)*SUM($D$2:D4)</f>
-        <v>93443.407500000001</v>
+        <v>14517622582.5</v>
       </c>
       <c r="G4">
         <f t="shared" si="0"/>
-        <v>0.42460425400618368</v>
+        <v>0.1786832402430425</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>5</v>
       </c>
       <c r="B5" s="1">
-        <v>45915.13</v>
+        <v>1099666663</v>
       </c>
       <c r="C5" s="1">
         <v>5</v>
       </c>
       <c r="D5" s="2">
-        <v>158029</v>
+        <v>23445275134</v>
       </c>
       <c r="E5">
         <f>(2/(A5*(A5-1)))*SUM($B$2:B5)</f>
-        <v>28397.394</v>
+        <v>1666400172.5</v>
       </c>
       <c r="F5">
         <f>(1/A5)*SUM($D$2:D5)</f>
-        <v>106360.52600000001</v>
+        <v>16303153092.800001</v>
       </c>
       <c r="G5">
         <f t="shared" si="0"/>
-        <v>0.26699185372588319</v>
+        <v>0.10221336713300791</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>6</v>
       </c>
       <c r="B6" s="1">
-        <v>37395.949999999997</v>
+        <v>910979559</v>
       </c>
       <c r="C6" s="1">
         <v>6</v>
       </c>
       <c r="D6" s="1">
-        <v>166548.20000000001</v>
+        <v>23633962238</v>
       </c>
       <c r="E6">
         <f>(2/(A6*(A6-1)))*SUM($B$2:B6)</f>
-        <v>21424.659333333333</v>
+        <v>1171665418.9333334</v>
       </c>
       <c r="F6">
         <f>(1/A6)*SUM($D$2:D6)</f>
-        <v>116391.80500000001</v>
+        <v>17524954617</v>
       </c>
       <c r="G6">
         <f t="shared" si="0"/>
-        <v>0.18407360667130587</v>
+        <v>6.6856973072943929E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>7</v>
       </c>
       <c r="B7" s="1">
-        <v>31452.23</v>
+        <v>732759003</v>
       </c>
       <c r="C7" s="1">
         <v>7</v>
       </c>
       <c r="D7" s="1">
-        <v>172491.9</v>
+        <v>23812182795</v>
       </c>
       <c r="E7">
         <f>(2/(A7*(A7-1)))*SUM($B$2:B7)</f>
-        <v>16801.053333333333</v>
+        <v>871797156.52380943</v>
       </c>
       <c r="F7">
         <f>(1/A7)*SUM($D$2:D7)</f>
-        <v>124406.10428571429</v>
+        <v>18423130071</v>
       </c>
       <c r="G7">
         <f t="shared" si="0"/>
-        <v>0.13505007193817112</v>
+        <v>4.7320794738138036E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>8</v>
       </c>
       <c r="B8" s="1">
-        <v>28364.2</v>
+        <v>698560553</v>
       </c>
       <c r="C8" s="1">
         <v>8</v>
       </c>
       <c r="D8" s="2">
-        <v>175580</v>
+        <v>23846381245</v>
       </c>
       <c r="E8">
         <f>(2/(A8*(A8-1)))*SUM($B$2:B8)</f>
-        <v>13613.797142857142</v>
+        <v>678796458.57142854</v>
       </c>
       <c r="F8">
         <f>(1/A8)*SUM($D$2:D8)</f>
-        <v>130802.84125000001</v>
+        <v>19101036467.75</v>
       </c>
       <c r="G8">
         <f t="shared" si="0"/>
-        <v>0.10407875710312325</v>
+        <v>3.5537153165353184E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>9</v>
       </c>
       <c r="B9" s="1">
-        <v>24009.13</v>
+        <v>550244473</v>
       </c>
       <c r="C9" s="1">
         <v>9</v>
       </c>
       <c r="D9" s="2">
-        <v>179935</v>
+        <v>23994697324</v>
       </c>
       <c r="E9">
         <f>(2/(A9*(A9-1)))*SUM($B$2:B9)</f>
-        <v>11255.429166666667</v>
+        <v>543237369.80555558</v>
       </c>
       <c r="F9">
         <f>(1/A9)*SUM($D$2:D9)</f>
-        <v>136261.97</v>
+        <v>19644776562.888889</v>
       </c>
       <c r="G9">
         <f t="shared" si="0"/>
-        <v>8.2601397636234572E-2</v>
+        <v>2.7653018504256742E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>10</v>
       </c>
       <c r="B10" s="1">
-        <v>20611.16</v>
+        <v>519843465</v>
       </c>
       <c r="C10" s="1">
         <v>10</v>
       </c>
       <c r="D10" s="2">
-        <v>183333</v>
+        <v>24025098333</v>
       </c>
       <c r="E10">
         <f>(2/(A10*(A10-1)))*SUM($B$2:B10)</f>
-        <v>9462.3691111111111</v>
+        <v>446141972.84444445</v>
       </c>
       <c r="F10">
         <f>(1/A10)*SUM($D$2:D10)</f>
-        <v>140969.073</v>
+        <v>20082808739.900002</v>
       </c>
       <c r="G10">
         <f t="shared" si="0"/>
-        <v>6.7123723734149196E-2</v>
+        <v>2.2215118344380842E-2</v>
       </c>
     </row>
   </sheetData>
